--- a/ig/nr-change-mss-Org/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/nr-change-mss-Org/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-15T11:25:47+00:00</t>
+    <t>2023-06-15T14:56:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-change-mss-Org/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/nr-change-mss-Org/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-15T14:56:56+00:00</t>
+    <t>2023-06-15T15:17:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-change-mss-Org/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/nr-change-mss-Org/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-15T15:17:55+00:00</t>
+    <t>2023-06-15T15:23:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
